--- a/site/Informations sur les entreprises.xlsx
+++ b/site/Informations sur les entreprises.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ameli\Documents\École\UQO\Réseaux informatiques et cybersécurité\A2025\INN1003-20 Projet intégrateur en innovation numérique\Pages html site web\2025-11-25 - Test à partir de python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{805D63FA-45A4-4F40-A940-6C6C9BEFF79B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E068BDD8-636D-402D-81CD-897F69D1E21E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,10 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="150">
-  <si>
-    <t>Membre de la chambre des commerces (oui ou non)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="149">
   <si>
     <t>Adresse</t>
   </si>
@@ -49,9 +46,6 @@
   </si>
   <si>
     <t>Longitude</t>
-  </si>
-  <si>
-    <t>Membre</t>
   </si>
   <si>
     <t>Secteur</t>
@@ -489,6 +483,9 @@
   </si>
   <si>
     <t>Nom de l'entreprise</t>
+  </si>
+  <si>
+    <t>Approuvée (oui ou non)</t>
   </si>
 </sst>
 </file>
@@ -623,7 +620,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -654,15 +651,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -684,45 +672,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="2">
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -752,20 +710,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{96935747-E663-4E4C-AEBC-6E2F5473DFBA}" name="Tableau2" displayName="Tableau2" ref="A1:M23" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:M23" xr:uid="{96935747-E663-4E4C-AEBC-6E2F5473DFBA}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{96935747-E663-4E4C-AEBC-6E2F5473DFBA}" name="Tableau2" displayName="Tableau2" ref="A1:L23" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:L23" xr:uid="{96935747-E663-4E4C-AEBC-6E2F5473DFBA}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L23">
     <sortCondition ref="A1:A23"/>
   </sortState>
-  <tableColumns count="13">
+  <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{F11D4C76-1F97-498D-8E78-E0FC30388EF9}" name="Nom de l'entreprise"/>
-    <tableColumn id="2" xr3:uid="{D91EEF8E-A9FC-4542-92ED-5B4B3116B87F}" name="Membre de la chambre des commerces (oui ou non)" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{30CF0375-C5C0-4D00-A579-E5B8FCB8C1A9}" name="Adresse"/>
     <tableColumn id="4" xr3:uid="{81F19807-37B3-488C-8249-14A494CA2FC9}" name="Contactée (oui ou non)"/>
+    <tableColumn id="2" xr3:uid="{554E1AC2-3ED2-458B-8244-6E22FBB65112}" name="Approuvée (oui ou non)"/>
     <tableColumn id="5" xr3:uid="{61E5698F-216D-42EE-BA80-3F1DD5C5130F}" name="Courriel" dataCellStyle="Hyperlink"/>
     <tableColumn id="6" xr3:uid="{D4864A46-8EDD-4F1F-81B4-FF04A3ED3D09}" name="Latitude"/>
     <tableColumn id="7" xr3:uid="{E806FCDF-E83D-4994-AFBC-84EB83C56B85}" name="Longitude"/>
-    <tableColumn id="8" xr3:uid="{A7BB0DBE-848A-4797-854E-FD40B64E6FFA}" name="Membre"/>
     <tableColumn id="9" xr3:uid="{22F6A84A-1B5C-4D3D-BCA1-080BDBB03EA7}" name="Secteur"/>
     <tableColumn id="10" xr3:uid="{0B079073-5E4B-420A-A091-95C7EF1CFFEB}" name="Description"/>
     <tableColumn id="11" xr3:uid="{F9A6D80F-8143-4741-A865-012D5D142D65}" name="Site internet" dataCellStyle="Hyperlink"/>
@@ -1109,792 +1066,722 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.28515625" customWidth="1"/>
-    <col min="2" max="2" width="26.5703125" style="21" customWidth="1"/>
-    <col min="3" max="3" width="49.42578125" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" customWidth="1"/>
+    <col min="2" max="2" width="49.42578125" customWidth="1"/>
+    <col min="3" max="4" width="11.85546875" customWidth="1"/>
     <col min="5" max="5" width="35.28515625" customWidth="1"/>
-    <col min="6" max="8" width="11.85546875" customWidth="1"/>
-    <col min="9" max="10" width="35.85546875" customWidth="1"/>
-    <col min="11" max="11" width="34.85546875" customWidth="1"/>
-    <col min="12" max="12" width="28.5703125" customWidth="1"/>
-    <col min="13" max="13" width="30.140625" customWidth="1"/>
+    <col min="6" max="7" width="11.85546875" customWidth="1"/>
+    <col min="8" max="9" width="35.85546875" customWidth="1"/>
+    <col min="10" max="10" width="34.85546875" customWidth="1"/>
+    <col min="11" max="11" width="28.5703125" customWidth="1"/>
+    <col min="12" max="12" width="30.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="23" customFormat="1" ht="54.75" customHeight="1">
-      <c r="A1" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="B1" s="23" t="s">
+    <row r="1" spans="1:12" s="20" customFormat="1" ht="54.75" customHeight="1">
+      <c r="A1" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="E1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="E1" s="24" t="s">
+      <c r="F1" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="23" t="s">
-        <v>148</v>
-      </c>
-      <c r="G1" s="23" t="s">
+      <c r="H1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="I1" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="J1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="23" t="s">
+      <c r="K1" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="L1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="K1" s="25" t="s">
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2">
+        <v>45.477446200000003</v>
+      </c>
+      <c r="G2">
+        <v>-75.781407900000005</v>
+      </c>
+      <c r="H2" t="s">
+        <v>113</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="60">
+      <c r="A3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F3">
+        <v>45.456288299999997</v>
+      </c>
+      <c r="G3">
+        <v>-75.691609299999996</v>
+      </c>
+      <c r="H3" t="s">
+        <v>101</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="K3" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="30">
+      <c r="A4" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="H4" t="s">
+        <v>83</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="K4" t="s">
+        <v>85</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="15.75">
+      <c r="A5" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F5">
+        <v>45.446864499999997</v>
+      </c>
+      <c r="G5">
+        <v>-75.741286400000007</v>
+      </c>
+      <c r="H5" t="s">
+        <v>118</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="K5" t="s">
+        <v>12</v>
+      </c>
+      <c r="L5" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6">
+        <v>45.515821099999997</v>
+      </c>
+      <c r="G6">
+        <v>-75.563872399999994</v>
+      </c>
+      <c r="H6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="H7" t="s">
+        <v>71</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="K7" t="s">
+        <v>19</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8">
+        <v>45.482286199999997</v>
+      </c>
+      <c r="G8">
+        <v>-75.687043599999996</v>
+      </c>
+      <c r="H8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K8" t="s">
+        <v>19</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="K9" t="s">
+        <v>78</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="24" customHeight="1">
+      <c r="A10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" t="s">
+        <v>106</v>
+      </c>
+      <c r="H10" t="s">
+        <v>107</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="K10" t="s">
+        <v>19</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" s="18" customFormat="1">
+      <c r="A11" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="M1" s="23" t="s">
+      <c r="B11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B2" s="18" t="s">
+      <c r="D11"/>
+      <c r="E11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="F2" s="28">
-        <v>45.477446200000003</v>
-      </c>
-      <c r="G2" s="28">
-        <v>-75.781407900000005</v>
-      </c>
-      <c r="I2" t="s">
-        <v>115</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="60">
-      <c r="A3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>101</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F3" s="29">
-        <v>45.456288299999997</v>
-      </c>
-      <c r="G3" s="29">
-        <v>-75.691609299999996</v>
-      </c>
-      <c r="I3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="F11">
+        <v>45.443578199999997</v>
+      </c>
+      <c r="G11">
+        <v>-75.738293299999995</v>
+      </c>
+      <c r="H11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11"/>
+      <c r="J11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K11" t="s">
+        <v>12</v>
+      </c>
+      <c r="L11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15.75">
+      <c r="A12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12">
+        <v>45.409162500000001</v>
+      </c>
+      <c r="G12">
+        <v>-75.777657899999994</v>
+      </c>
+      <c r="L12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="150">
+      <c r="A13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="L13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="K14" t="s">
+        <v>34</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15">
+        <v>45.417415499999997</v>
+      </c>
+      <c r="G15">
+        <v>-75.760478000000006</v>
+      </c>
+      <c r="H15" t="s">
+        <v>43</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="K15" t="s">
+        <v>34</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" t="s">
         <v>36</v>
       </c>
-      <c r="M3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="30">
-      <c r="A4" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="I4" t="s">
-        <v>85</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="L4" t="s">
+      <c r="B16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16">
+        <v>45.462529000000004</v>
+      </c>
+      <c r="G16">
+        <v>-75.737071700000001</v>
+      </c>
+      <c r="L16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="135">
+      <c r="A17" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="18"/>
+      <c r="E17" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I17" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="J17" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="K17" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L17" s="24" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H18" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="K18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="B19" s="2" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="15.75">
-      <c r="A5" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="F5" s="30">
-        <v>45.446864499999997</v>
-      </c>
-      <c r="G5" s="30">
-        <v>-75.741286400000007</v>
-      </c>
-      <c r="I5" t="s">
-        <v>120</v>
-      </c>
-      <c r="K5" s="5" t="s">
+      <c r="C19" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F19">
+        <v>45.537975299999999</v>
+      </c>
+      <c r="G19">
+        <v>-75.763172800000007</v>
+      </c>
+      <c r="H19" t="s">
+        <v>43</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="30.75">
+      <c r="A20" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="L5" t="s">
-        <v>14</v>
-      </c>
-      <c r="M5" t="s">
+      <c r="B20" s="2" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="31">
-        <v>45.515821099999997</v>
-      </c>
-      <c r="G6" s="31">
-        <v>-75.563872399999994</v>
-      </c>
-      <c r="I6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="L6" t="s">
-        <v>21</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="4" t="s">
+      <c r="C20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="17" t="s">
         <v>70</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="I7" t="s">
-        <v>73</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="L7" t="s">
-        <v>21</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="32">
-        <v>45.482286199999997</v>
-      </c>
-      <c r="G8" s="32">
-        <v>-75.687043599999996</v>
-      </c>
-      <c r="I8" t="s">
-        <v>19</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="L8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="I9" t="s">
-        <v>45</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="L9" t="s">
-        <v>80</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="24" customHeight="1">
-      <c r="A10" t="s">
-        <v>106</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="D10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" t="s">
-        <v>108</v>
-      </c>
-      <c r="I10" t="s">
-        <v>109</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="L10" t="s">
-        <v>21</v>
-      </c>
-      <c r="M10" s="16" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" s="21" customFormat="1">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="33">
-        <v>45.443578199999997</v>
-      </c>
-      <c r="G11" s="33">
-        <v>-75.738293299999995</v>
-      </c>
-      <c r="H11"/>
-      <c r="I11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J11"/>
-      <c r="K11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L11" t="s">
-        <v>14</v>
-      </c>
-      <c r="M11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="15.75">
-      <c r="A12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="34">
-        <v>45.409162500000001</v>
-      </c>
-      <c r="G12" s="34">
-        <v>-75.777657899999994</v>
-      </c>
-      <c r="M12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="150">
-      <c r="A13" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="M13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="L14" t="s">
-        <v>36</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" t="s">
-        <v>49</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F15" s="35">
-        <v>45.417415499999997</v>
-      </c>
-      <c r="G15" s="35">
-        <v>-75.760478000000006</v>
-      </c>
-      <c r="I15" t="s">
-        <v>45</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="L15" t="s">
-        <v>36</v>
-      </c>
-      <c r="M15" s="16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="A16" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F16" s="36">
-        <v>45.462529000000004</v>
-      </c>
-      <c r="G16" s="36">
-        <v>-75.737071700000001</v>
-      </c>
-      <c r="M16" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="135">
-      <c r="A17" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="D17" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="J17" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="K17" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="L17" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="M17" s="27" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
-      <c r="A18" t="s">
-        <v>65</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" t="s">
-        <v>66</v>
-      </c>
-      <c r="D18" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="I18" t="s">
-        <v>19</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="L18" t="s">
-        <v>21</v>
-      </c>
-      <c r="M18" s="6" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
-      <c r="A19" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="B19" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D19" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="F19" s="37">
-        <v>45.537975299999999</v>
-      </c>
-      <c r="G19" s="37">
-        <v>-75.763172800000007</v>
-      </c>
-      <c r="I19" t="s">
-        <v>45</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="M19" s="6" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="30.75">
-      <c r="A20" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D20" t="s">
-        <v>9</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>72</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="J20" s="2"/>
-      <c r="K20" s="8" t="s">
+      <c r="H20" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I20" s="2"/>
+      <c r="J20" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" s="2" customFormat="1" ht="15.75">
+      <c r="A21" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="L20" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M20" s="2" t="s">
+      <c r="B21" s="15" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" s="2" customFormat="1" ht="15.75">
-      <c r="A21" s="14" t="s">
+      <c r="C21" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21"/>
+      <c r="E21" s="5" t="s">
         <v>127</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="D21" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>129</v>
       </c>
       <c r="F21"/>
       <c r="G21"/>
-      <c r="H21"/>
-      <c r="I21" t="s">
-        <v>120</v>
-      </c>
-      <c r="J21"/>
-      <c r="K21" s="5" t="s">
+      <c r="H21" t="s">
+        <v>118</v>
+      </c>
+      <c r="I21"/>
+      <c r="J21" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="K21" t="s">
+        <v>129</v>
+      </c>
+      <c r="L21" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="L21" t="s">
-        <v>131</v>
-      </c>
-      <c r="M21" s="6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="75">
+    </row>
+    <row r="22" spans="1:12" ht="75">
       <c r="A22" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" t="s">
+        <v>93</v>
+      </c>
+      <c r="E22" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="B22" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="F22">
+        <v>45.484167999999997</v>
+      </c>
+      <c r="G22">
+        <v>-75.642858000000004</v>
+      </c>
+      <c r="H22" t="s">
         <v>95</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="J22" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="F22" s="38">
-        <v>45.484167999999997</v>
-      </c>
-      <c r="G22" s="38">
-        <v>-75.642858000000004</v>
-      </c>
-      <c r="I22" t="s">
+      <c r="K22" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" t="s">
         <v>97</v>
       </c>
-      <c r="K22" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="L22" t="s">
-        <v>36</v>
-      </c>
-      <c r="M22" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" t="s">
+      <c r="F23">
+        <v>45.458995999999999</v>
+      </c>
+      <c r="G23">
+        <v>-75.734533400000004</v>
+      </c>
+      <c r="H23" t="s">
         <v>43</v>
       </c>
-      <c r="D23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E23" s="5" t="s">
+      <c r="J23" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F23" s="39">
-        <v>45.458995999999999</v>
-      </c>
-      <c r="G23" s="39">
-        <v>-75.734533400000004</v>
-      </c>
-      <c r="I23" t="s">
+      <c r="K23" t="s">
         <v>45</v>
       </c>
-      <c r="K23" s="5" t="s">
+      <c r="L23" t="s">
         <v>46</v>
-      </c>
-      <c r="L23" t="s">
-        <v>47</v>
-      </c>
-      <c r="M23" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E11" r:id="rId1" xr:uid="{2422D141-439E-42F2-9F27-E0337955DBF7}"/>
-    <hyperlink ref="K11" r:id="rId2" xr:uid="{5A1FC66F-B41B-41C5-94BF-9922C5E5617C}"/>
+    <hyperlink ref="J11" r:id="rId2" xr:uid="{5A1FC66F-B41B-41C5-94BF-9922C5E5617C}"/>
     <hyperlink ref="E6" r:id="rId3" xr:uid="{28834344-D466-4B63-ABEE-592E1504CB73}"/>
-    <hyperlink ref="K6" r:id="rId4" xr:uid="{F6D7A718-B879-4A5C-BE46-6DAF248624F3}"/>
+    <hyperlink ref="J6" r:id="rId4" xr:uid="{F6D7A718-B879-4A5C-BE46-6DAF248624F3}"/>
     <hyperlink ref="E12" r:id="rId5" xr:uid="{5475CBF9-7FF4-4BBF-9146-0E0915C64876}"/>
     <hyperlink ref="E8" r:id="rId6" xr:uid="{F597B002-1F72-4916-9BE8-C5CB426303DD}"/>
-    <hyperlink ref="K8" r:id="rId7" xr:uid="{B0FADCE6-EF23-45BD-A24F-6DFAA39CB8C8}"/>
+    <hyperlink ref="J8" r:id="rId7" xr:uid="{B0FADCE6-EF23-45BD-A24F-6DFAA39CB8C8}"/>
     <hyperlink ref="E16" r:id="rId8" xr:uid="{1355C6C6-9571-44A0-9C9D-A99EBCD5C2D9}"/>
     <hyperlink ref="E14" r:id="rId9" xr:uid="{B703CB01-CD6A-4BB6-AC70-BA6516F8C06E}"/>
-    <hyperlink ref="K14" r:id="rId10" xr:uid="{3B110CEC-884A-49E3-9916-033244A5E2A7}"/>
+    <hyperlink ref="J14" r:id="rId10" xr:uid="{3B110CEC-884A-49E3-9916-033244A5E2A7}"/>
     <hyperlink ref="E23" r:id="rId11" xr:uid="{FE893918-037E-4B76-BBC5-EAE73B54905F}"/>
     <hyperlink ref="E15" r:id="rId12" xr:uid="{C5AC9E72-6ECE-4515-98EF-9F14C0C6B1DE}"/>
-    <hyperlink ref="K15" r:id="rId13" xr:uid="{E5439625-E99D-4EB8-A280-815DD01AB3E4}"/>
+    <hyperlink ref="J15" r:id="rId13" xr:uid="{E5439625-E99D-4EB8-A280-815DD01AB3E4}"/>
     <hyperlink ref="E13" r:id="rId14" xr:uid="{1A20B356-51DF-4B68-A438-EA451429F163}"/>
     <hyperlink ref="E17" r:id="rId15" xr:uid="{0B907429-67A8-4F68-80ED-4EE5D2267262}"/>
-    <hyperlink ref="K17" r:id="rId16" xr:uid="{CD7D280A-640F-4371-BBE6-D9D79A407C4A}"/>
+    <hyperlink ref="J17" r:id="rId16" xr:uid="{CD7D280A-640F-4371-BBE6-D9D79A407C4A}"/>
     <hyperlink ref="E18" r:id="rId17" xr:uid="{9B5A7E48-BD94-4CA8-A9DA-A5391BDA37CE}"/>
-    <hyperlink ref="K18" r:id="rId18" xr:uid="{E608465A-851C-4379-B382-072B4759C9F7}"/>
-    <hyperlink ref="K7" r:id="rId19" xr:uid="{5BD1C4E5-7C8B-45D8-9FBF-3ECC737964B8}"/>
-    <hyperlink ref="K9" r:id="rId20" xr:uid="{22C82502-8AE2-4A2A-A3EB-A209C19E6812}"/>
+    <hyperlink ref="J18" r:id="rId18" xr:uid="{E608465A-851C-4379-B382-072B4759C9F7}"/>
+    <hyperlink ref="J7" r:id="rId19" xr:uid="{5BD1C4E5-7C8B-45D8-9FBF-3ECC737964B8}"/>
+    <hyperlink ref="J9" r:id="rId20" xr:uid="{22C82502-8AE2-4A2A-A3EB-A209C19E6812}"/>
     <hyperlink ref="E9" r:id="rId21" xr:uid="{63666CA8-3929-40C4-82E5-DC0F6FE6D7F2}"/>
     <hyperlink ref="E19" r:id="rId22" xr:uid="{0442F197-4347-4E81-B35D-286C681DCF0B}"/>
-    <hyperlink ref="K19" r:id="rId23" xr:uid="{6B0D780A-621C-42AB-B4B1-EFA19241EBA1}"/>
+    <hyperlink ref="J19" r:id="rId23" xr:uid="{6B0D780A-621C-42AB-B4B1-EFA19241EBA1}"/>
     <hyperlink ref="E3" r:id="rId24" xr:uid="{70EF57F3-F5C6-48F3-A06D-A04587CEB969}"/>
     <hyperlink ref="E2" r:id="rId25" xr:uid="{FCB86395-C3A6-4BBB-A234-ED8893EC10BE}"/>
-    <hyperlink ref="K23" r:id="rId26" xr:uid="{327E33DB-51A4-4B61-814C-A7D01AF3256F}"/>
+    <hyperlink ref="J23" r:id="rId26" xr:uid="{327E33DB-51A4-4B61-814C-A7D01AF3256F}"/>
     <hyperlink ref="E5" r:id="rId27" xr:uid="{FCD14BD4-31C4-443E-8809-6A9624B9E3DE}"/>
-    <hyperlink ref="K20" r:id="rId28" xr:uid="{5B604B43-3883-4791-896B-92A516B25065}"/>
+    <hyperlink ref="J20" r:id="rId28" xr:uid="{5B604B43-3883-4791-896B-92A516B25065}"/>
     <hyperlink ref="E4" r:id="rId29" xr:uid="{52411AE9-B4EB-4BD0-B7BA-199F6CB45A8C}"/>
-    <hyperlink ref="K4" r:id="rId30" xr:uid="{02D7EBBE-83E6-44BA-86E9-2B0F14FD806F}"/>
-    <hyperlink ref="K5" r:id="rId31" xr:uid="{63429850-AE9F-419D-A103-28B5AA0AE469}"/>
-    <hyperlink ref="K2" r:id="rId32" xr:uid="{280D6625-44D4-4428-B687-B95B48BFC9D9}"/>
+    <hyperlink ref="J4" r:id="rId30" xr:uid="{02D7EBBE-83E6-44BA-86E9-2B0F14FD806F}"/>
+    <hyperlink ref="J5" r:id="rId31" xr:uid="{63429850-AE9F-419D-A103-28B5AA0AE469}"/>
+    <hyperlink ref="J2" r:id="rId32" xr:uid="{280D6625-44D4-4428-B687-B95B48BFC9D9}"/>
     <hyperlink ref="E21" r:id="rId33" xr:uid="{500539D7-538E-49D6-BDF0-8407229DFD0C}"/>
-    <hyperlink ref="K21" r:id="rId34" xr:uid="{B4E28BC2-8C42-463F-BCDA-14E623A7292C}"/>
-    <hyperlink ref="K3" r:id="rId35" xr:uid="{19832A3C-F9D0-43FD-85B6-0393201B2076}"/>
-    <hyperlink ref="K10" r:id="rId36" xr:uid="{E23F2A0B-3CBB-4B0E-96FE-5D104EC59EE1}"/>
-    <hyperlink ref="K22" r:id="rId37" xr:uid="{08420B69-7CA5-4DF7-9BB4-B8E4D635088B}"/>
-    <hyperlink ref="K13" r:id="rId38" display="https://laboiteagrains.com/?utm_source=google&amp;utm_medium=cpc&amp;utm_campaign=20061135833&amp;utm_term=&amp;gad_source=1&amp;gad_campaignid=20546142671&amp;gbraid=0AAAAAC47fwpXMBgWvD333kYbA1B-Kf1n_&amp;gclid=CjwKCAiAlfvIBhA6EiwAcErpyXM8XNHRMJLpPV0lh1sPKrf4iNru6FZr1IchfcYnhwChBryXZ_W91BoCQIwQAvD_BwE" xr:uid="{0440DE8D-55EE-4A6F-82DA-4D00E6B45F5A}"/>
+    <hyperlink ref="J21" r:id="rId34" xr:uid="{B4E28BC2-8C42-463F-BCDA-14E623A7292C}"/>
+    <hyperlink ref="J3" r:id="rId35" xr:uid="{19832A3C-F9D0-43FD-85B6-0393201B2076}"/>
+    <hyperlink ref="J10" r:id="rId36" xr:uid="{E23F2A0B-3CBB-4B0E-96FE-5D104EC59EE1}"/>
+    <hyperlink ref="J22" r:id="rId37" xr:uid="{08420B69-7CA5-4DF7-9BB4-B8E4D635088B}"/>
+    <hyperlink ref="J13" r:id="rId38" display="https://laboiteagrains.com/?utm_source=google&amp;utm_medium=cpc&amp;utm_campaign=20061135833&amp;utm_term=&amp;gad_source=1&amp;gad_campaignid=20546142671&amp;gbraid=0AAAAAC47fwpXMBgWvD333kYbA1B-Kf1n_&amp;gclid=CjwKCAiAlfvIBhA6EiwAcErpyXM8XNHRMJLpPV0lh1sPKrf4iNru6FZr1IchfcYnhwChBryXZ_W91BoCQIwQAvD_BwE" xr:uid="{0440DE8D-55EE-4A6F-82DA-4D00E6B45F5A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -1917,64 +1804,64 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="105">
+      <c r="A3" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="C2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="C3" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="E3" s="18" t="s">
         <v>137</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="105">
-      <c r="A3" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>146</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -1986,26 +1873,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="b250b3cb-ed05-4be6-b17d-4ae3244c258e" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5331aa49-e235-437d-8feb-49bdb5f17d15">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010092DAE86864467945942620C2C350F511" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="abc950134318b6f42b61679069c1824b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5331aa49-e235-437d-8feb-49bdb5f17d15" xmlns:ns3="b250b3cb-ed05-4be6-b17d-4ae3244c258e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a14525766d6ea579ccc21a2a31d85c66" ns2:_="" ns3:_="">
     <xsd:import namespace="5331aa49-e235-437d-8feb-49bdb5f17d15"/>
@@ -2194,26 +2061,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7886DF9-576B-4B17-BD47-9970127BB8DF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b250b3cb-ed05-4be6-b17d-4ae3244c258e"/>
-    <ds:schemaRef ds:uri="5331aa49-e235-437d-8feb-49bdb5f17d15"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b250b3cb-ed05-4be6-b17d-4ae3244c258e" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5331aa49-e235-437d-8feb-49bdb5f17d15">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4288B9C-F452-454A-AE98-9420758E352B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CDD27B61-247A-4FB0-8F8E-5D64C1343DC7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2230,4 +2098,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7886DF9-576B-4B17-BD47-9970127BB8DF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b250b3cb-ed05-4be6-b17d-4ae3244c258e"/>
+    <ds:schemaRef ds:uri="5331aa49-e235-437d-8feb-49bdb5f17d15"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4288B9C-F452-454A-AE98-9420758E352B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>